--- a/output/pdf_financials_xlsx/USA.xlsx
+++ b/output/pdf_financials_xlsx/USA.xlsx
@@ -6022,46 +6022,46 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-3.219</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>10.054</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>8.398999999999999</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>7.788</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>6.454</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>6.284</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>6.541</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>6.695</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>6.842</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>6.833</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>9.797000000000001</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>8.324999999999999</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>14.426</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>13.459</v>
       </c>
     </row>
     <row r="92">
@@ -12308,7 +12308,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -28492,7 +28496,11 @@
           <t>Foreign currency translation reserve 7,974</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/USA.xlsx
+++ b/output/pdf_financials_xlsx/USA.xlsx
@@ -1074,10 +1074,10 @@
         <v>-0.029</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.066</v>
+        <v>0.153</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2103,10 +2103,10 @@
         <v>11.072</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-9.343999999999999</v>
+        <v>-9.563000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-65.944</v>
+        <v>-66.03</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-20.038</v>
@@ -2225,10 +2225,10 @@
         <v>11.072</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-9.343999999999999</v>
+        <v>-9.563000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-65.944</v>
+        <v>-66.03</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-20.038</v>
@@ -2286,10 +2286,10 @@
         <v>24.17203362078376</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-30.92708436765631</v>
+        <v>-31.65193790752325</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-209.4856888719464</v>
+        <v>-209.7588868769656</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-37.48924228250702</v>
@@ -2467,7 +2467,7 @@
         <v>6.739973</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>25.768</v>
@@ -2589,7 +2589,7 @@
         <v>6.739973</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>25.768</v>
@@ -3321,7 +3321,7 @@
         <v>7.001646</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>16.128</v>
@@ -8013,22 +8013,22 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-3.353</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-3.227</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-3.392</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-2.681</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.679</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="125">
@@ -8074,22 +8074,22 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-3.353</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-3.227</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-3.392</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-2.681</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.679</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="126">
@@ -31590,7 +31590,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -34328,7 +34328,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -39942,7 +39942,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -84412,7 +84416,7 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">

--- a/output/pdf_financials_xlsx/USA.xlsx
+++ b/output/pdf_financials_xlsx/USA.xlsx
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -59072,7 +59072,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/USA.xlsx
+++ b/output/pdf_financials_xlsx/USA.xlsx
@@ -1379,10 +1379,10 @@
         <v>-3.953</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-12.751</v>
+        <v>12.751</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0.652</v>
@@ -1391,7 +1391,7 @@
         <v>0.21</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.427</v>
+        <v>-0.427</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>0.668</v>
@@ -1400,16 +1400,16 @@
         <v>1.958</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.741</v>
+        <v>-1.002</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1.708</v>
+        <v>-1.61</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.977</v>
+        <v>3.718</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>0.184</v>
+        <v>-2.06</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>0.679</v>
@@ -2368,16 +2368,16 @@
         <v>-6.06529954773558</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-2.385090768636539</v>
+        <v>-3.225183468520664</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-1.053111859223361</v>
+        <v>-0.9926874082843155</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-2.355976753719646</v>
+        <v>-8.965733439436688</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.4573360176969155</v>
+        <v>-5.120174980737206</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>-1.405069839627522</v>
@@ -2842,43 +2842,43 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.292</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.425</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>5.928</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>3.611</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>3.265</v>
       </c>
     </row>
     <row r="41">
@@ -2903,43 +2903,43 @@
         <v>8.791</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8.288</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>9.294</v>
+        <v>9.586</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>4.529</v>
+        <v>4.864</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.002</v>
+        <v>4.24</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>6.631</v>
+        <v>6.732</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>7.712</v>
+        <v>7.833</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>5.269</v>
+        <v>5.342</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>5.102</v>
+        <v>5.527</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>8.208</v>
+        <v>8.457000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>11.552</v>
+        <v>17.48</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>9.486000000000001</v>
+        <v>13.097</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>7.132</v>
+        <v>10.692</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.856</v>
+        <v>12.121</v>
       </c>
     </row>
     <row r="42">
@@ -3330,43 +3330,43 @@
         <v>7.453</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>8.039</v>
+        <v>7.957</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.093</v>
+        <v>2.801</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.203</v>
+        <v>0.868</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.888</v>
+        <v>1.65</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.869</v>
+        <v>0.768</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.094</v>
+        <v>9.973000000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.499</v>
+        <v>2.426</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.2</v>
+        <v>1.775</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.426</v>
+        <v>2.177</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.832</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.876</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>4.357</v>
+        <v>1.092</v>
       </c>
     </row>
     <row r="49">
@@ -7445,7 +7445,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -8336,40 +8336,26 @@
       <c r="F129" s="3" t="n">
         <v>0.646</v>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="3" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>2.127</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>26.486</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>10.494</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>4.265</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>24.376</v>
       </c>
       <c r="N129" s="3" t="n">
         <v>73.973</v>
@@ -8386,10 +8372,8 @@
       <c r="R129" s="3" t="n">
         <v>35.121</v>
       </c>
-      <c r="S129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S129" s="3" t="n">
+        <v>182.896</v>
       </c>
     </row>
     <row r="130">
@@ -8722,40 +8706,26 @@
       <c r="F135" s="3" t="n">
         <v>10.296</v>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="3" t="n">
+        <v>2.446</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>10.393</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>5.387</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>8.638</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>14.143</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-18.921</v>
@@ -8772,10 +8742,8 @@
       <c r="R135" s="3" t="n">
         <v>-3.068</v>
       </c>
-      <c r="S135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S135" s="3" t="n">
+        <v>-3.945</v>
       </c>
     </row>
   </sheetData>
@@ -39358,7 +39326,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -44080,7 +44052,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -45916,7 +45892,11 @@
           <t>Sandstorm private placement</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -47288,7 +47268,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -48020,7 +48004,11 @@
           <t>Share issuance from private placement</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -48526,7 +48514,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -50106,7 +50098,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -51572,7 +51568,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -51886,7 +51886,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -53858,7 +53862,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -54278,7 +54286,11 @@
           <t>Proceeds from long-term investments</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -55224,7 +55236,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -62262,7 +62278,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr">
         <is>
           <t>-</t>
@@ -71816,7 +71836,11 @@
           <t>Income tax recovery (expense) (Note 25)</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E608" t="inlineStr">
         <is>
           <t>-</t>
@@ -73980,7 +74004,11 @@
           <t>Income tax recovery (expense) (Note 23)</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
           <t>-</t>
@@ -76386,7 +76414,11 @@
           <t>Income tax recovery (expense) (Note 22)</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E653" t="inlineStr">
         <is>
           <t>-</t>
@@ -77518,7 +77550,11 @@
           <t>Income tax recovery (Note 24)</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
           <t>-</t>
@@ -80484,7 +80520,11 @@
           <t>Income tax recovery (expense) (Note 18)</t>
         </is>
       </c>
-      <c r="D693" t="inlineStr"/>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E693" t="inlineStr">
         <is>
           <t>-</t>
@@ -82474,7 +82514,11 @@
           <t>Income tax recovery (expense) (Note 17)</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E712" t="inlineStr">
         <is>
           <t>-</t>
@@ -84824,7 +84868,11 @@
           <t>Income tax recovery (expense) (Note 19)</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E735" t="inlineStr">
         <is>
           <t>-</t>
@@ -86388,7 +86436,11 @@
           <t>Income tax (recovery) expense (Note 17)</t>
         </is>
       </c>
-      <c r="D750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E750" t="inlineStr">
         <is>
           <t>-</t>
@@ -94588,7 +94640,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D828" t="inlineStr"/>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E828" s="5" t="n">
         <v>-90.699167</v>
       </c>
